--- a/Result/profitability/3694.xlsx
+++ b/Result/profitability/3694.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.75</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16875</v>
+        <v>1.1525</v>
       </c>
       <c r="N2" t="n">
-        <v>15.02125</v>
+        <v>14.9225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>5.1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.69</v>
+        <v>1.7125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.23125</v>
+        <v>15.10125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6375</v>
+        <v>1.64125</v>
       </c>
       <c r="N4" t="n">
-        <v>15.59125</v>
+        <v>15.44</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.02</v>
       </c>
       <c r="M5" t="n">
-        <v>1.66875</v>
+        <v>1.635</v>
       </c>
       <c r="N5" t="n">
-        <v>16.6875</v>
+        <v>16.6825</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.98</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6575</v>
+        <v>1.57875</v>
       </c>
       <c r="N6" t="n">
-        <v>17.28875</v>
+        <v>17.24625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.61875</v>
+        <v>1.62375</v>
       </c>
       <c r="N7" t="n">
-        <v>18.12375</v>
+        <v>17.955</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>1.67375</v>
+        <v>1.64625</v>
       </c>
       <c r="N8" t="n">
-        <v>18.73625</v>
+        <v>18.63625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3694</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2887</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2484</v>
+      </c>
+      <c r="E73" t="n">
+        <v>403</v>
+      </c>
+      <c r="F73" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G73" t="n">
+        <v>101</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3.48%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>28</v>
+      </c>
+      <c r="J73" t="n">
+        <v>129</v>
+      </c>
+      <c r="K73" t="n">
+        <v>123</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.9249999999999999</v>
+      </c>
+      <c r="N73" t="n">
+        <v>14.64625</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.2156862745098039</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>-0.8000000000000007</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.05423728813559325</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.2523364485981309</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-0.04000000000000092</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>-0.002859185132237374</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
